--- a/qc/spreadsheets/trust_qc.xlsx
+++ b/qc/spreadsheets/trust_qc.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'runs'!$A$1:$Y$653</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'thresholds'!$A$1:$K$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'thresholds'!$A$1:$M$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24308,7 +24308,7 @@
         <v>0.282051282051282</v>
       </c>
       <c r="L261" t="n">
-        <v>99.92029332058027</v>
+        <v>99.92162176523726</v>
       </c>
       <c r="M261" t="b">
         <v>0</v>
@@ -24399,7 +24399,7 @@
         <v>0.2666666666666667</v>
       </c>
       <c r="L262" t="n">
-        <v>99.88575375949839</v>
+        <v>99.82198841596259</v>
       </c>
       <c r="M262" t="b">
         <v>0</v>
@@ -24490,7 +24490,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="L263" t="n">
-        <v>99.91365109729529</v>
+        <v>99.92427865455124</v>
       </c>
       <c r="M263" t="b">
         <v>0</v>
@@ -24581,7 +24581,7 @@
         <v>0.4</v>
       </c>
       <c r="L264" t="n">
-        <v>99.92693554386524</v>
+        <v>99.91763643126627</v>
       </c>
       <c r="M264" t="b">
         <v>0</v>
@@ -25410,7 +25410,7 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="L273" t="n">
-        <v>99.8193315266486</v>
+        <v>99.82730219459057</v>
       </c>
       <c r="M273" t="b">
         <v>0</v>
@@ -25501,7 +25501,7 @@
         <v>0.1842105263157895</v>
       </c>
       <c r="L274" t="n">
-        <v>99.79674796747967</v>
+        <v>99.78346352090972</v>
       </c>
       <c r="M274" t="b">
         <v>0</v>
@@ -27513,7 +27513,7 @@
         <v>0.3571428571428572</v>
       </c>
       <c r="L296" t="n">
-        <v>99.91896487592327</v>
+        <v>99.8512141984165</v>
       </c>
       <c r="M296" t="b">
         <v>0</v>
@@ -27604,7 +27604,7 @@
         <v>0.4193548387096774</v>
       </c>
       <c r="L297" t="n">
-        <v>99.89638131675434</v>
+        <v>99.79010574419469</v>
       </c>
       <c r="M297" t="b">
         <v>0</v>
@@ -60591,20 +60591,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -60615,50 +60617,60 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>bids_tasks</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>q1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>q3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>iqr</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>lower_fence</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>upper_fence</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>outlier_direction</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>n_outliers</t>
         </is>
@@ -60677,33 +60689,43 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>tsnr</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>652</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>23.67533069654019</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>39.23382612285786</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>15.55849542631768</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.3375875570636708</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>62.57156926233438</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>lower</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -60720,33 +60742,43 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>fd_mean</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>652</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>0.1243403939943806</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>0.245970697395569</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.1216303034011884</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>-0.05810506110740206</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>0.4284161524973517</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>upper</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>48</v>
       </c>
     </row>
@@ -60763,33 +60795,43 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>tedana_rejected_components</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>652</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>9.75</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>22</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>12.25</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>-8.625</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>40.375</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>upper</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>65</v>
       </c>
     </row>
@@ -60806,38 +60848,48 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>trust</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>brain_coverage_pct</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>652</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>99.61209416015728</v>
       </c>
-      <c r="F5" t="n">
-        <v>99.9096657633243</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.2975716031670146</v>
-      </c>
       <c r="H5" t="n">
-        <v>99.16573675540675</v>
+        <v>99.90866942983156</v>
       </c>
       <c r="I5" t="n">
-        <v>100.3560231680748</v>
-      </c>
-      <c r="J5" t="inlineStr">
+        <v>0.2965752696742783</v>
+      </c>
+      <c r="J5" t="n">
+        <v>99.16723125564587</v>
+      </c>
+      <c r="K5" t="n">
+        <v>100.353532334343</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>lower</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>25</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K5"/>
+  <autoFilter ref="A1:M5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>